--- a/public/storageExcel/PCS.xlsx
+++ b/public/storageExcel/PCS.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>PCS编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -33,14 +33,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>所属园区</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>所属站点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>安装地址</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -81,10 +73,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>站点1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>正泰大厦</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -97,7 +85,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>正泰量测科技园</t>
+    <t>所属储能柜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>储能柜1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -423,27 +415,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5546875" customWidth="1"/>
     <col min="2" max="2" width="11.77734375" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" customWidth="1"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" customWidth="1"/>
-    <col min="11" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="21.109375" customWidth="1"/>
-    <col min="14" max="14" width="13.33203125" customWidth="1"/>
-    <col min="15" max="15" width="18.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" customWidth="1"/>
+    <col min="6" max="6" width="7.109375" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="21.109375" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -454,43 +445,40 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>110</v>
       </c>
@@ -498,42 +486,39 @@
         <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>10</v>
+      </c>
+      <c r="I2">
+        <v>200</v>
+      </c>
+      <c r="J2">
+        <v>220</v>
+      </c>
+      <c r="K2">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2">
-        <v>100</v>
-      </c>
-      <c r="I2">
-        <v>10</v>
-      </c>
-      <c r="J2">
+      <c r="L2">
+        <v>220</v>
+      </c>
+      <c r="M2">
         <v>200</v>
       </c>
-      <c r="K2">
-        <v>220</v>
-      </c>
-      <c r="L2">
-        <v>15</v>
-      </c>
-      <c r="M2">
-        <v>220</v>
-      </c>
       <c r="N2">
-        <v>200</v>
-      </c>
-      <c r="O2">
         <v>80</v>
       </c>
     </row>
